--- a/lorenzo-playwright-kdf/excelFramework/testcases/R&R/LSTP_R&R_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/R&R/LSTP_R&R_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssivasubram9\ORBIS PAS UKI-LZO (1)\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\R&amp;R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B554FDC-65CB-467C-9726-4BB7AB643C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97882A57-8709-49C0-B8E7-D1BA3EC6387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0646128-2D85-4E82-864C-5394E95B0A8D}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B0646128-2D85-4E82-864C-5394E95B0A8D}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -2197,7 +2197,7 @@
         <v>236</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>237</v>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AD2" s="31">
         <f ca="1">NOW()</f>
-        <v>46168.404869675927</v>
+        <v>46220.872282407407</v>
       </c>
       <c r="AE2" t="s">
         <v>184</v>
@@ -6764,4 +6764,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/R&R/LSTP_R&R_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/R&R/LSTP_R&R_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\R&amp;R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97882A57-8709-49C0-B8E7-D1BA3EC6387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BF9BC4-A399-426C-B511-28F89848BAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B0646128-2D85-4E82-864C-5394E95B0A8D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B0646128-2D85-4E82-864C-5394E95B0A8D}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="454">
   <si>
     <t>StepNo</t>
   </si>
@@ -1411,6 +1411,9 @@
   </si>
   <si>
     <t>12.21</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2621,7 +2624,7 @@
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>14</v>
+        <v>453</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -2694,7 +2697,7 @@
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6" t="s">
-        <v>14</v>
+        <v>453</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -6503,7 +6506,7 @@
       </c>
       <c r="AD2" s="31">
         <f ca="1">NOW()</f>
-        <v>46220.872282407407</v>
+        <v>46235.435005902778</v>
       </c>
       <c r="AE2" t="s">
         <v>184</v>
